--- a/ig/DM-SEPTEMBRE-2025/alignement-nuva-bdpm.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/alignement-nuva-bdpm.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="619">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.946</t>
+    <t>1.0.992</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04</t>
+    <t>2025-09-08</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,6 +282,24 @@
     <t>ENGERIX B 10 microgrammes/0,5 mL, suspension injectable en seringue préremplie. Vaccin de l'hépatite B (ADNr), (adsorbé) (VHB)</t>
   </si>
   <si>
+    <t>VAC0230</t>
+  </si>
+  <si>
+    <t>FLUAD</t>
+  </si>
+  <si>
+    <t>64090291</t>
+  </si>
+  <si>
+    <t>FLUAD suspension injectable en seringue préremplie.Vaccin antigrippal (antigènes de surface, inactivé, avec adjuvant)</t>
+  </si>
+  <si>
+    <t>3400930304716</t>
+  </si>
+  <si>
+    <t>FLUAD suspension injectable en seringue préremplie.Vaccin antigrippal (antigènes de surface, inactivé, avec adjuvant) 1 seringue préremplie en verre de 0,5 mL avec aiguille</t>
+  </si>
+  <si>
     <t>VAC0040</t>
   </si>
   <si>
@@ -420,6 +438,24 @@
     <t>ROTATEQ, solution buvable. Vaccin Rotavirus (vivant, oral) 1 tube unidose souple polyéthylène basse densité (PEBD) suremballée(s)/surpochée(s) de 2 ml</t>
   </si>
   <si>
+    <t>VAC0926</t>
+  </si>
+  <si>
+    <t>FLUCELVAX TRIVALENT</t>
+  </si>
+  <si>
+    <t>62752472</t>
+  </si>
+  <si>
+    <t>FLUCELVAX suspension injectable en seringue préremplie. Vaccin antigrippal inactivé (antigène de surface, préparé sur cultures cellulaires)</t>
+  </si>
+  <si>
+    <t>3400930304686</t>
+  </si>
+  <si>
+    <t>FLUCELVAX suspension injectable en seringue préremplie. Vaccin antigrippal inactivé (antigène de surface, préparé sur cultures cellulaires) 1 seringue préremplie en verre de 0,5 mL avec aiguille</t>
+  </si>
+  <si>
     <t>VAC0166</t>
   </si>
   <si>
@@ -849,7 +885,7 @@
     <t>VAC0649</t>
   </si>
   <si>
-    <t>EFLUELDA QIV-HD</t>
+    <t>EFLUELDA TETRA</t>
   </si>
   <si>
     <t>67823603</t>
@@ -1566,6 +1602,24 @@
     <t>PRIORIX, poudre et solvant pour solution injectable en seringue préremplie. Vaccin rougeoleux, des oreillons et rubéoleux vivant</t>
   </si>
   <si>
+    <t>VAC0016</t>
+  </si>
+  <si>
+    <t>INFLUVAC</t>
+  </si>
+  <si>
+    <t>3400930296165</t>
+  </si>
+  <si>
+    <t>INFLUVAC, suspension injectable en seringue préremplie. Vaccin grippal inactivé à antigènes de surface 1 seringue(s) préremplie(s) en verre de 0,5 ml avec aiguille(s)</t>
+  </si>
+  <si>
+    <t>63156183</t>
+  </si>
+  <si>
+    <t>INFLUVAC, suspension injectable en seringue préremplie. Vaccin grippal inactivé à antigènes de surface</t>
+  </si>
+  <si>
     <t>VAC0011</t>
   </si>
   <si>
@@ -1774,12 +1828,6 @@
   </si>
   <si>
     <t>STAMARIL, poudre et solvant pour suspension injectable en seringue préremplie. Vaccin de la fièvre jaune (Vivant) 1 flacon(s) en verre de 1 dose(s) - 1 seringue(s) préremplie(s) en verre de 0,5 ml avec deux aiguille(s) séparées</t>
-  </si>
-  <si>
-    <t>3400935081018</t>
-  </si>
-  <si>
-    <t>STAMARIL, poudre et solvant pour suspension injectable en seringue préremplie. Vaccin de la fièvre jaune (Vivant) 1 flacon(s) en verre de 1 dose(s) - 1 seringue(s) préremplie(s) en verre de 0,5 ml avec 1 aiguille(s) attachée</t>
   </si>
   <si>
     <t>VAC0030</t>
@@ -2091,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2674,27 +2722,27 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D35" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="B35" t="s" s="2">
+      <c r="E35" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>132</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>36</v>
@@ -2878,53 +2926,53 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50">
@@ -2938,10 +2986,10 @@
         <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51">
@@ -2955,18 +3003,18 @@
         <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>36</v>
@@ -2980,10 +3028,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>36</v>
@@ -3082,27 +3130,27 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D59" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="B59" t="s" s="2">
+      <c r="E59" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D59" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="E59" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>36</v>
@@ -3116,27 +3164,27 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D61" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="B61" t="s" s="2">
+      <c r="E61" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>36</v>
@@ -3235,27 +3283,27 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D68" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="B68" t="s" s="2">
+      <c r="E68" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D68" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>36</v>
@@ -3269,10 +3317,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>36</v>
@@ -3286,61 +3334,61 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>36</v>
@@ -3354,10 +3402,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>36</v>
@@ -3405,27 +3453,27 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>36</v>
@@ -3439,78 +3487,78 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>36</v>
@@ -3524,10 +3572,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>36</v>
@@ -3541,27 +3589,27 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D86" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="B86" t="s" s="2">
+      <c r="E86" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D86" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="E86" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>36</v>
@@ -3660,27 +3708,27 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D93" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="B93" t="s" s="2">
+      <c r="E93" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D93" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="E93" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>36</v>
@@ -3694,10 +3742,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>36</v>
@@ -3728,27 +3776,27 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>36</v>
@@ -3762,10 +3810,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>36</v>
@@ -4017,27 +4065,27 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>36</v>
@@ -4051,27 +4099,27 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>36</v>
@@ -4085,10 +4133,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>36</v>
@@ -4102,27 +4150,27 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>36</v>
@@ -4136,27 +4184,27 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>36</v>
@@ -4170,10 +4218,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>36</v>
@@ -4799,27 +4847,27 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>36</v>
@@ -4833,27 +4881,27 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>36</v>
@@ -4867,10 +4915,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>36</v>
@@ -5071,27 +5119,27 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D176" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="B176" t="s" s="2">
+      <c r="E176" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D176" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="E176" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>36</v>
@@ -5105,27 +5153,27 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D178" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="B178" t="s" s="2">
+      <c r="E178" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D178" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="E178" t="s" s="2">
-        <v>554</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>36</v>
@@ -5139,27 +5187,27 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D180" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="B180" t="s" s="2">
+      <c r="E180" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D180" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="E180" t="s" s="2">
-        <v>560</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>36</v>
@@ -5275,155 +5323,240 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C191" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E191" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C192" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E192" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C193" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E193" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C194" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E194" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C195" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E195" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C196" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E196" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D197" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="E197" t="s" s="2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="E198" t="s" s="2">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D199" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="E199" t="s" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="E200" t="s" s="2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="E201" t="s" s="2">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
